--- a/School_docs/Premchand Mahto Inter College/Commerce/session 2026-28 - commerce.xlsx
+++ b/School_docs/Premchand Mahto Inter College/Commerce/session 2026-28 - commerce.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="35">
   <si>
     <t>ROLL NO.</t>
   </si>
@@ -112,6 +112,15 @@
   </si>
   <si>
     <t>STUDENT'S NAME</t>
+  </si>
+  <si>
+    <t>TANIYA KUMARI</t>
+  </si>
+  <si>
+    <t>ANAND MAHLI</t>
+  </si>
+  <si>
+    <t>LALITA DEVI</t>
   </si>
 </sst>
 </file>
@@ -473,7 +482,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="2"/>
@@ -698,6 +707,35 @@
         <v>636356180044</v>
       </c>
       <c r="J7" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E8" s="3">
+        <v>40308</v>
+      </c>
+      <c r="G8" s="2">
+        <v>9304608558</v>
+      </c>
+      <c r="H8" s="1">
+        <v>603194521810</v>
+      </c>
+      <c r="I8" s="1">
+        <v>684528716726</v>
+      </c>
+      <c r="J8" s="2" t="s">
         <v>30</v>
       </c>
     </row>
